--- a/deliverables/Worship Music School - Song Library.xlsx
+++ b/deliverables/Worship Music School - Song Library.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Song Library" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Song Library'!$A$3:$O$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Song Library'!$A$3:$R$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,6 +606,21 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Chart URL</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Chord Chart URL</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Reference Track URL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -671,6 +686,9 @@
           <t>The gold-standard starter worship song.</t>
         </is>
       </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -736,6 +754,9 @@
           <t>Simple, powerful; capo-friendly for guitar.</t>
         </is>
       </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -801,6 +822,9 @@
           <t>Classic, easy, on-theme lyrics.</t>
         </is>
       </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -866,6 +890,9 @@
           <t>Breathy lead vocal; leave room.</t>
         </is>
       </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -931,6 +958,9 @@
           <t>Big chorus vocal; very easy bass.</t>
         </is>
       </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -996,6 +1026,9 @@
           <t>Simple, singable, testimony song.</t>
         </is>
       </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1061,6 +1094,9 @@
           <t>Great for keys players to lead.</t>
         </is>
       </c>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1126,6 +1162,9 @@
           <t>Simple parts, big dynamic build.</t>
         </is>
       </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1191,6 +1230,9 @@
           <t>Key change &amp; vocal range at the end.</t>
         </is>
       </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1256,6 +1298,9 @@
           <t>Tests timing discipline.</t>
         </is>
       </c>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1321,6 +1366,9 @@
           <t>Current #1; vocal range is the challenge.</t>
         </is>
       </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1386,6 +1434,9 @@
           <t>From whisper to wall of sound.</t>
         </is>
       </c>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1451,6 +1502,9 @@
           <t>Great vocal-harmony teaching song.</t>
         </is>
       </c>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1516,6 +1570,9 @@
           <t>Solid pocket, big chorus.</t>
         </is>
       </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1581,6 +1638,9 @@
           <t>Simple chords, room to improvise.</t>
         </is>
       </c>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1646,6 +1706,9 @@
           <t>Repetitive on purpose; lock the groove.</t>
         </is>
       </c>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1711,6 +1774,9 @@
           <t>Fun, celebratory.</t>
         </is>
       </c>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1776,6 +1842,9 @@
           <t>Keys carry the intro.</t>
         </is>
       </c>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1841,6 +1910,9 @@
           <t>Rewards a band that can wait.</t>
         </is>
       </c>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1906,6 +1978,9 @@
           <t>Soft verses, full chorus.</t>
         </is>
       </c>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1971,6 +2046,9 @@
           <t>Builds to a declaration.</t>
         </is>
       </c>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2036,6 +2114,9 @@
           <t>Fun, feel-forward.</t>
         </is>
       </c>
+      <c r="P25" s="4" t="inlineStr"/>
+      <c r="Q25" s="4" t="inlineStr"/>
+      <c r="R25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2101,6 +2182,9 @@
           <t>Simple chords, big payoff.</t>
         </is>
       </c>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2166,6 +2250,9 @@
           <t>The vocal moment is everything.</t>
         </is>
       </c>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2231,6 +2318,9 @@
           <t>A vocal showcase.</t>
         </is>
       </c>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2296,6 +2386,9 @@
           <t>Dynamics discipline.</t>
         </is>
       </c>
+      <c r="P29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2361,6 +2454,9 @@
           <t>Powerful, patient arrangement.</t>
         </is>
       </c>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2426,6 +2522,9 @@
           <t>Advanced dynamics across ~6 min.</t>
         </is>
       </c>
+      <c r="P31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2491,6 +2590,9 @@
           <t>Tricky but joyful; stretch goal.</t>
         </is>
       </c>
+      <c r="P32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2556,6 +2658,9 @@
           <t>Beautiful and simple; great closer.</t>
         </is>
       </c>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2621,6 +2726,9 @@
           <t>Easy full-band win.</t>
         </is>
       </c>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2686,6 +2794,9 @@
           <t>High energy opener.</t>
         </is>
       </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2751,6 +2862,9 @@
           <t>Congregation favorite.</t>
         </is>
       </c>
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2816,6 +2930,9 @@
           <t>Fun vocal feature.</t>
         </is>
       </c>
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2881,6 +2998,9 @@
           <t>For a confident lead vocalist.</t>
         </is>
       </c>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -2946,6 +3066,9 @@
           <t>Everyone knows it; I–vi–IV–V forever.</t>
         </is>
       </c>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr"/>
+      <c r="R39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -3011,6 +3134,9 @@
           <t>Simple and universally known.</t>
         </is>
       </c>
+      <c r="P40" s="8" t="inlineStr"/>
+      <c r="Q40" s="8" t="inlineStr"/>
+      <c r="R40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -3076,6 +3202,9 @@
           <t>Teaches the off-beat; super positive.</t>
         </is>
       </c>
+      <c r="P41" s="8" t="inlineStr"/>
+      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -3141,6 +3270,9 @@
           <t>Gentle, easy, sweet.</t>
         </is>
       </c>
+      <c r="P42" s="8" t="inlineStr"/>
+      <c r="Q42" s="8" t="inlineStr"/>
+      <c r="R42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -3206,6 +3338,9 @@
           <t>Great acoustic-guitar song.</t>
         </is>
       </c>
+      <c r="P43" s="8" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -3271,6 +3406,9 @@
           <t>High-energy, fun to play.</t>
         </is>
       </c>
+      <c r="P44" s="8" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -3336,6 +3474,9 @@
           <t>Bass &amp; keys challenge.</t>
         </is>
       </c>
+      <c r="P45" s="8" t="inlineStr"/>
+      <c r="Q45" s="8" t="inlineStr"/>
+      <c r="R45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -3401,6 +3542,9 @@
           <t>Everybody-locks-in tune.</t>
         </is>
       </c>
+      <c r="P46" s="8" t="inlineStr"/>
+      <c r="Q46" s="8" t="inlineStr"/>
+      <c r="R46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -3466,6 +3610,9 @@
           <t>Horn-line energy; hard but a blast.</t>
         </is>
       </c>
+      <c r="P47" s="8" t="inlineStr"/>
+      <c r="Q47" s="8" t="inlineStr"/>
+      <c r="R47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -3531,12 +3678,15 @@
           <t>Bass is the boss; ultimate stretch goal.</t>
         </is>
       </c>
+      <c r="P48" s="8" t="inlineStr"/>
+      <c r="Q48" s="8" t="inlineStr"/>
+      <c r="R48" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O48"/>
+  <autoFilter ref="A3:R48"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G48">
     <cfRule type="colorScale" priority="1">
